--- a/exports/高二（14）班座位表_2026-10-20.xlsx
+++ b/exports/高二（14）班座位表_2026-10-20.xlsx
@@ -123,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -263,13 +263,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E5E5E5"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E5E5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E5E5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E5E5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -359,6 +373,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -735,35 +752,35 @@
       <c r="P1" s="2" t="n"/>
     </row>
     <row r="2" ht="40" customHeight="1" s="26">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>韩寅</t>
         </is>
       </c>
       <c r="B2" s="23" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="35" t="inlineStr">
         <is>
           <t>邱守诺</t>
         </is>
       </c>
       <c r="D2" s="22" t="n"/>
-      <c r="E2" s="3" t="n"/>
+      <c r="E2" s="35" t="n"/>
       <c r="F2" s="23" t="n"/>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="35" t="inlineStr">
         <is>
           <t>吕凯文</t>
         </is>
       </c>
       <c r="H2" s="23" t="n"/>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="35" t="inlineStr">
         <is>
           <t>包智翔</t>
         </is>
       </c>
       <c r="J2" s="23" t="n"/>
-      <c r="K2" s="3" t="n"/>
+      <c r="K2" s="35" t="n"/>
       <c r="L2" s="23" t="n"/>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="35" t="inlineStr">
         <is>
           <t>朱宏文</t>
         </is>
@@ -807,43 +824,43 @@
       <c r="AB3" s="2" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1" s="26">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>吕洲</t>
         </is>
       </c>
       <c r="B4" s="23" t="n"/>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>潘智宸</t>
         </is>
       </c>
       <c r="D4" s="23" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>刘雨昊</t>
         </is>
       </c>
       <c r="F4" s="23" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>张铭泽</t>
         </is>
       </c>
       <c r="H4" s="23" t="n"/>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t>章何弈</t>
         </is>
       </c>
       <c r="J4" s="23" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t>王宇轩</t>
         </is>
       </c>
       <c r="L4" s="23" t="n"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="35" t="inlineStr">
         <is>
           <t>葛立文</t>
         </is>
@@ -889,43 +906,43 @@
       <c r="AB5" s="2" t="n"/>
     </row>
     <row r="6" ht="40" customHeight="1" s="26">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>滕欣然</t>
         </is>
       </c>
       <c r="B6" s="23" t="n"/>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>王安冉</t>
         </is>
       </c>
       <c r="D6" s="23" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>江文槿</t>
         </is>
       </c>
       <c r="F6" s="23" t="n"/>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>许子言</t>
         </is>
       </c>
       <c r="H6" s="23" t="n"/>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t>雍涵茜</t>
         </is>
       </c>
       <c r="J6" s="23" t="n"/>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="35" t="inlineStr">
         <is>
           <t>胡佳馨</t>
         </is>
       </c>
       <c r="L6" s="23" t="n"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="35" t="inlineStr">
         <is>
           <t>路永延</t>
         </is>
@@ -970,43 +987,43 @@
       <c r="AB7" s="2" t="n"/>
     </row>
     <row r="8" ht="40" customHeight="1" s="26">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>管欣然</t>
         </is>
       </c>
       <c r="B8" s="23" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>韩珂馨</t>
         </is>
       </c>
       <c r="D8" s="23" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>陈亦可</t>
         </is>
       </c>
       <c r="F8" s="23" t="n"/>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>郭玥橦</t>
         </is>
       </c>
       <c r="H8" s="25" t="n"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="35" t="inlineStr">
         <is>
           <t>袁雨霏</t>
         </is>
       </c>
       <c r="J8" s="23" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="35" t="inlineStr">
         <is>
           <t>陈瑞可</t>
         </is>
       </c>
       <c r="L8" s="23" t="n"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="35" t="inlineStr">
         <is>
           <t>吴子晗</t>
         </is>
@@ -1051,43 +1068,43 @@
       <c r="AB9" s="2" t="n"/>
     </row>
     <row r="10" ht="40" customHeight="1" s="26">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>解紫萱</t>
         </is>
       </c>
       <c r="B10" s="23" t="n"/>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>赵丝格</t>
         </is>
       </c>
       <c r="D10" s="23" t="n"/>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>严雨萱</t>
         </is>
       </c>
       <c r="F10" s="23" t="n"/>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t>焦子萱</t>
         </is>
       </c>
       <c r="H10" s="23" t="n"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="35" t="inlineStr">
         <is>
           <t>朱嘉仪</t>
         </is>
       </c>
       <c r="J10" s="23" t="n"/>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="35" t="inlineStr">
         <is>
           <t>黄子涵</t>
         </is>
       </c>
       <c r="L10" s="23" t="n"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="35" t="inlineStr">
         <is>
           <t>王欣欣</t>
         </is>
@@ -1131,43 +1148,43 @@
       <c r="AB11" s="2" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1" s="26">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>李瑶瑶</t>
         </is>
       </c>
       <c r="B12" s="23" t="n"/>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>赵许琪</t>
         </is>
       </c>
       <c r="D12" s="23" t="n"/>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>任佳艳</t>
         </is>
       </c>
       <c r="F12" s="23" t="n"/>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>纪吴仪</t>
         </is>
       </c>
       <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="35" t="inlineStr">
         <is>
           <t>徐文萱</t>
         </is>
       </c>
       <c r="J12" s="23" t="n"/>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="35" t="inlineStr">
         <is>
           <t>曹秋瑾</t>
         </is>
       </c>
       <c r="L12" s="23" t="n"/>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="35" t="inlineStr">
         <is>
           <t>李紫涵</t>
         </is>
@@ -1185,23 +1202,50 @@
       <c r="AB12" s="3" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1" s="26"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="27" t="inlineStr">
         <is>
           <t>讲     台</t>
         </is>
       </c>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="29" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="26">
       <c r="C16" s="19" t="n"/>
+      <c r="D16" s="30" t="n"/>
+      <c r="J16" s="31" t="n"/>
       <c r="M16" s="19" t="n"/>
     </row>
-    <row r="17"/>
-    <row r="18"/>
+    <row r="17">
+      <c r="D17" s="30" t="n"/>
+      <c r="J17" s="31" t="n"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="33" t="n"/>
+      <c r="F18" s="33" t="n"/>
+      <c r="G18" s="33" t="n"/>
+      <c r="H18" s="33" t="n"/>
+      <c r="I18" s="33" t="n"/>
+      <c r="J18" s="34" t="n"/>
+    </row>
+    <row r="19"/>
     <row r="20" ht="14" customHeight="1" s="26"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24" ht="18" customHeight="1" s="26">
       <c r="K24" s="9" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="P28" s="5" t="n"/>
     </row>

--- a/exports/高二（14）班座位表_2026-10-20.xlsx
+++ b/exports/高二（14）班座位表_2026-10-20.xlsx
@@ -123,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -277,13 +277,14 @@
         <color rgb="00E5E5E5"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -374,6 +375,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -764,7 +768,7 @@
         </is>
       </c>
       <c r="D2" s="22" t="n"/>
-      <c r="E2" s="35" t="n"/>
+      <c r="E2" s="36" t="n"/>
       <c r="F2" s="23" t="n"/>
       <c r="G2" s="35" t="inlineStr">
         <is>
@@ -778,7 +782,7 @@
         </is>
       </c>
       <c r="J2" s="23" t="n"/>
-      <c r="K2" s="35" t="n"/>
+      <c r="K2" s="36" t="n"/>
       <c r="L2" s="23" t="n"/>
       <c r="M2" s="35" t="inlineStr">
         <is>
